--- a/工作-大圣牌/战棋/盘丝洞手牌&法强.xlsx
+++ b/工作-大圣牌/战棋/盘丝洞手牌&法强.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\GitHub\Notes\工作-大圣牌\战棋\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:10000001_{B5EE1230-FA38-4036-B941-A6FADE955661}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28EB0ED5-82AD-48B1-9A73-91CFEC505628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{1608F9AB-8F1D-4234-B19D-459BE5F65858}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{1608F9AB-8F1D-4234-B19D-459BE5F65858}"/>
   </bookViews>
   <sheets>
     <sheet name="手牌，法强" sheetId="1" r:id="rId1"/>
-    <sheet name="挤爆" sheetId="2" r:id="rId2"/>
+    <sheet name="残念" sheetId="3" r:id="rId2"/>
+    <sheet name="挤爆" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="93">
   <si>
     <t>归属阵营</t>
   </si>
@@ -221,11 +221,6 @@
     <t>登场：释放记住的法术2次</t>
   </si>
   <si>
-    <t>通过残念/使用等方式使在部署区/手牌区的盘丝洞部将获得buff，通过残念拉出手牌中获得buff的部将，又或是传统下毒阵容。
-也提供一定的法强接口来支持养酒馆/记忆九转金丹的可能神通玩法</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>列2</t>
   </si>
   <si>
@@ -299,9 +294,6 @@
   </si>
   <si>
     <t>后援：消灭左侧相邻的盘丝洞部将并重新召唤</t>
-  </si>
-  <si>
-    <t>如果该效果触发了龙魂的额外身材赋予效果，则也只持续到该回合的战斗结束</t>
   </si>
   <si>
     <t>后援：消灭相邻的盘丝洞部将并重新召唤</t>
@@ -357,6 +349,11 @@
   <si>
     <t>每回合前2次购买神通时，获得1张记录了该神通的紫霞门徒</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>通过残念/使用等方式使在部署区/手牌区的盘丝洞部将获得buff，通过残念拉出手牌中获得buff的部将，又或是传统下毒阵容。
+也提供一定的法强接口来支持养商店/记忆九转金丹的可能神通玩法</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1010,7 +1007,7 @@
       </c>
       <c r="K2" s="5"/>
       <c r="M2" s="13" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="N2" s="14"/>
       <c r="O2" s="14"/>
@@ -1473,7 +1470,7 @@
       </c>
       <c r="C19" s="4"/>
       <c r="D19" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>34</v>
@@ -1590,7 +1587,7 @@
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>40</v>
@@ -1616,7 +1613,7 @@
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
       <c r="E25" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F25" s="4">
         <v>5</v>
@@ -1776,10 +1773,10 @@
       </c>
       <c r="C32" s="4"/>
       <c r="D32" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F32" s="4">
         <v>6</v>
@@ -1802,7 +1799,7 @@
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
       <c r="E33" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F33" s="4">
         <v>6</v>
@@ -1824,7 +1821,7 @@
       </c>
       <c r="C34" s="4"/>
       <c r="D34" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>48</v>
@@ -1872,10 +1869,10 @@
       </c>
       <c r="C36" s="4"/>
       <c r="D36" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F36" s="4">
         <v>6</v>
@@ -1898,7 +1895,7 @@
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
       <c r="E37" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F37" s="4">
         <v>6</v>
@@ -2119,6 +2116,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ACD78D1-C03F-4A45-9109-E8025382171F}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetData/>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE073880-5114-4E20-890B-98D0E47C14EC}">
   <dimension ref="A1:L52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -2165,20 +2172,20 @@
         <v>10</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="16.5">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="8" t="s">
         <v>56</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>57</v>
       </c>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
@@ -2204,13 +2211,13 @@
     </row>
     <row r="4" spans="1:12" ht="16.5">
       <c r="C4" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="E4" s="11" t="s">
         <v>59</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>60</v>
       </c>
       <c r="L4" s="4"/>
     </row>
@@ -2224,7 +2231,7 @@
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F5" s="4">
         <v>1</v>
@@ -2246,7 +2253,7 @@
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F6" s="4">
         <v>1</v>
@@ -2268,7 +2275,7 @@
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F7" s="4">
         <v>1</v>
@@ -2310,7 +2317,7 @@
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F9" s="4">
         <v>2</v>
@@ -2352,7 +2359,7 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F11" s="4">
         <v>2</v>
@@ -2394,7 +2401,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F13" s="4">
         <v>3</v>
@@ -2416,7 +2423,7 @@
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F14" s="4">
         <v>3</v>
@@ -2438,7 +2445,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F15" s="4">
         <v>3</v>
@@ -2460,7 +2467,7 @@
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F16" s="4">
         <v>3</v>
@@ -2481,10 +2488,10 @@
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>69</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>70</v>
       </c>
       <c r="F17" s="4">
         <v>3</v>
@@ -2526,7 +2533,7 @@
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
       <c r="E19" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F19" s="4">
         <v>3</v>
@@ -2568,7 +2575,7 @@
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
       <c r="E21" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F21" s="4">
         <v>4</v>
@@ -2577,7 +2584,7 @@
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
       <c r="J21" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K21" s="5"/>
       <c r="L21" s="4"/>
@@ -2612,7 +2619,7 @@
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
       <c r="E23" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F23" s="4">
         <v>4</v>
@@ -2654,7 +2661,7 @@
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
       <c r="E25" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F25" s="4">
         <v>5</v>
@@ -2696,7 +2703,7 @@
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
       <c r="E27" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F27" s="4">
         <v>5</v>
@@ -2738,7 +2745,7 @@
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
       <c r="E29" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F29" s="4">
         <v>5</v>
@@ -2780,7 +2787,7 @@
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
       <c r="E31" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F31" s="4">
         <v>6</v>
@@ -2822,7 +2829,7 @@
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
       <c r="E33" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F33" s="4">
         <v>6</v>
@@ -2844,7 +2851,7 @@
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
       <c r="E34" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F34" s="4">
         <v>6</v>
@@ -2866,7 +2873,7 @@
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
       <c r="E35" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F35" s="4">
         <v>6</v>
@@ -2874,9 +2881,7 @@
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
       <c r="I35" s="4"/>
-      <c r="J35" s="4" t="s">
-        <v>79</v>
-      </c>
+      <c r="J35" s="4"/>
       <c r="K35" s="5"/>
       <c r="L35" s="4"/>
     </row>
@@ -2890,7 +2895,7 @@
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
       <c r="E36" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F36" s="4">
         <v>6</v>
